--- a/xls/square_16_tri3_23.xlsx
+++ b/xls/square_16_tri3_23.xlsx
@@ -482,13 +482,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-2.294197910396919</v>
+        <v>-2.2941974460113155</v>
       </c>
       <c r="J23">
-        <v>-1.8830848357270664</v>
+        <v>-1.883085012577816</v>
       </c>
       <c r="K23">
-        <v>2.8387537642422958</v>
+        <v>2.8387537675279733</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-1.9846439379494087</v>
+        <v>-1.9846440689072655</v>
       </c>
       <c r="J24">
-        <v>-1.5646154691458918</v>
+        <v>-1.5646154467899127</v>
       </c>
       <c r="K24">
-        <v>3.0599528659952457</v>
+        <v>3.059952867505606</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.9934812592806375</v>
+        <v>-0.9934812070913526</v>
       </c>
       <c r="J25">
-        <v>-0.8370133217108262</v>
+        <v>-0.8370132824561952</v>
       </c>
       <c r="K25">
-        <v>3.734645121788352</v>
+        <v>3.734645111842554</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.3202806748748627</v>
+        <v>-0.3202806613431685</v>
       </c>
       <c r="J26">
-        <v>-0.2380711752898319</v>
+        <v>-0.23807116729443267</v>
       </c>
       <c r="K26">
-        <v>3.8455317692965556</v>
+        <v>3.8455317581831983</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>0.00042430403971411825</v>
+        <v>0.0004243041078750111</v>
       </c>
       <c r="J27">
-        <v>-0.0005071229492401765</v>
+        <v>-0.0005071229130602162</v>
       </c>
       <c r="K27">
-        <v>3.0234626568332588</v>
+        <v>3.0234626559655764</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0014701837130017847</v>
+        <v>-0.001470183706281675</v>
       </c>
       <c r="J28">
-        <v>-0.0012058639603127984</v>
+        <v>-0.0012058639560918536</v>
       </c>
       <c r="K28">
-        <v>2.9257840589328366</v>
+        <v>2.925784058358238</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.0016524003437168862</v>
+        <v>-0.001652400337733366</v>
       </c>
       <c r="J29">
-        <v>-0.001383728728793004</v>
+        <v>-0.0013837287253007206</v>
       </c>
       <c r="K29">
-        <v>2.95646513106619</v>
+        <v>2.9564651308961514</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.0006646435393754504</v>
+        <v>-0.0006646435428221165</v>
       </c>
       <c r="J30">
-        <v>-0.0005112287230704944</v>
+        <v>-0.0005112287249488516</v>
       </c>
       <c r="K30">
-        <v>2.7099268647734536</v>
+        <v>2.709926865019715</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-0.0012352134723269306</v>
+        <v>-0.0012352134702011569</v>
       </c>
       <c r="J31">
-        <v>-0.0010007882681759943</v>
+        <v>-0.0010007882665036658</v>
       </c>
       <c r="K31">
-        <v>2.864894758405333</v>
+        <v>2.864894757947708</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -797,13 +797,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.0003408268012318222</v>
+        <v>-0.00034082680130502387</v>
       </c>
       <c r="J32">
-        <v>-0.0002744921241080733</v>
+        <v>-0.0002744921241525087</v>
       </c>
       <c r="K32">
-        <v>2.5918153399444046</v>
+        <v>2.5918153397557275</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_23.xlsx
+++ b/xls/square_16_tri3_23.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>576</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>289</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>1.8660191546834983</v>
+      </c>
+      <c r="J21">
+        <v>-1.3524901943340628</v>
+      </c>
+      <c r="K21">
+        <v>2.5756432126784468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>576</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>289</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-1.4017491866201985</v>
+      </c>
+      <c r="J22">
+        <v>-2.0099620898558777</v>
+      </c>
+      <c r="K22">
+        <v>1.5219696616164926</v>
+      </c>
+    </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>11</v>
